--- a/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
+++ b/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
@@ -1146,7 +1146,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>第3章第5節　介護人材</t>
+          <t>第2章第6節　介護人材</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>3施設すべてが回答しており未回答による差ではない。見える化の介護職員は令和4年度78人から令和5年度56人・令和6年度59人へ減っており、調査値77人は令和4年度の水準に近い。見える化の直近2年の値が実態より低いか、調査で介護職員の範囲を広く記入したかのいずれかである。第3章第5節で従事者数の推移を記述する前に確認を要する。</t>
+          <t>3施設すべてが回答しており未回答による差ではない。見える化の介護職員は令和4年度78人から令和5年度56人・令和6年度59人へ減っており、調査値77人は令和4年度の水準に近い。見える化の直近2年の値が実態より低いか、調査で介護職員の範囲を広く記入したかのいずれかである。第2章第6節で従事者数の推移を記述する前に確認を要する。</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
-          <t>13事業所のうち回答3事業所（うち1事業所はNo.1の重複の疑い）。見える化の従事者数は平成29年度（訪問介護員53人）が最後であり、令和6年度の値がない。第3章第5節の訪問介護の人材は今回の調査のみが根拠となる。</t>
+          <t>13事業所のうち回答3事業所（うち1事業所はNo.1の重複の疑い）。見える化の従事者数は平成29年度（訪問介護員53人）が最後であり、令和6年度の値がない。第2章第6節の訪問介護の人材は今回の調査のみが根拠となる。</t>
         </is>
       </c>
     </row>
@@ -12196,7 +12196,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>2事業所の職員を単純に合計すると13人が二重に計上される。同じ構造の「有料老人ホームびえいの郷（1人）とシルバーハウス訪問介護事業所（13人）」は分けて記入されており、サービス付高齢者住宅ゆうも0人である。住宅型有料老人ホームは介護保険の指定サービスではなく、見える化のK系列にも従事者数の系列にも現れない（10シート）。併設の訪問介護が介護を提供する形であれば、実数は訪問系の13人であり、有料老人ホーム華の13人は重複となる。受託者は、訪問系13人を実数とし有料側を重複として除いた348人を用いることを案とする。実数を照会のうえ確定する。令和8年8月5日に受領したグループホームびえいの郷の公表画面により、シルバーハウス株式会社は訪問介護（美瑛町大町2丁目5番28号）とグループホーム（同5番14号）を別の所在地で運営し、住宅型有料老人ホームびえいの郷は訪問介護と同じ5番28号にあることが確認された。併設の訪問介護が介護を提供する構造が裏付けられた。令和8年8月6日に受領したヘルパーステーションフラワーの公表画面（記入日 令和7年10月29日）により、訪問介護員等の実人数13人・常勤8人・非常勤5人、前年度の採用者数7人・退職者数2人が確認された。調査の訪問系の票と実人数・常勤・非常勤・採用・離職のすべてが一致する。訪問介護事業所の側の13人が実在の値であることが裏づけられた（住まいと施設の公表名簿との突合 11シート）。ただし公表制度の対象は指定サービスであり、有料老人ホーム華（住宅型有料老人ホーム）は対象外であるため、華の側が0であることを公表データで確かめることはできない。確定にはなお提出元への確認を要する。なお、同じ構造の株式会社オレンジサポート（住宅型有料老人ホームひばりの森・グループホームひばり・指定訪問介護事業所ひばりが同一敷地）については、施設票の9人（常勤7・非常勤2・採用3・離職0）と訪問介護の公表画面の12人（常勤11・非常勤1・採用0・退職1）が異なる数値であり、転記ではない。ただし訪問介護12人のうち11人が兼務であるため、施設票の職員との重複の有無は確かめられていない。</t>
+          <t>2事業所の職員を単純に合計すると13人が二重に計上される。同じ構造の「有料老人ホームびえいの郷（1人）とシルバーハウス訪問介護事業所（13人）」は分けて記入されており、サービス付高齢者住宅ゆうも0人である。住宅型有料老人ホームは介護保険の指定サービスではなく、見える化のK系列にも従事者数の系列にも現れない（10シート）。併設の訪問介護が介護を提供する形であれば、実数は訪問系の13人であり、有料老人ホーム華の13人は重複となる。受託者は、訪問系13人を実数とし有料側を重複として除いた348人を用いることを案とする。実数を照会のうえ確定する。確定した数値は第2章第6節（介護人材）の介護職員数に用いる。令和8年8月5日に受領したグループホームびえいの郷の公表画面により、シルバーハウス株式会社は訪問介護（美瑛町大町2丁目5番28号）とグループホーム（同5番14号）を別の所在地で運営し、住宅型有料老人ホームびえいの郷は訪問介護と同じ5番28号にあることが確認された。併設の訪問介護が介護を提供する構造が裏付けられた。令和8年8月6日に受領したヘルパーステーションフラワーの公表画面（記入日 令和7年10月29日）により、訪問介護員等の実人数13人・常勤8人・非常勤5人、前年度の採用者数7人・退職者数2人が確認された。調査の訪問系の票と実人数・常勤・非常勤・採用・離職のすべてが一致する。訪問介護事業所の側の13人が実在の値であることが裏づけられた（住まいと施設の公表名簿との突合 11シート）。ただし公表制度の対象は指定サービスであり、有料老人ホーム華（住宅型有料老人ホーム）は対象外であるため、華の側が0であることを公表データで確かめることはできない。確定にはなお提出元への確認を要する。なお、同じ構造の株式会社オレンジサポート（住宅型有料老人ホームひばりの森・グループホームひばり・指定訪問介護事業所ひばりが同一敷地）については、施設票の9人（常勤7・非常勤2・採用3・離職0）と訪問介護の公表画面の12人（常勤11・非常勤1・採用0・退職1）が異なる数値であり、転記ではない。ただし訪問介護12人のうち11人が兼務であるため、施設票の職員との重複の有無は確かめられていない。</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>第2章第6節</t>
         </is>
       </c>
     </row>
@@ -13141,7 +13141,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>3事業所の介護職員が集計に含まれていない。提出の有無を確認する。第3章第5節（人材）の従事者数に影響する。</t>
+          <t>3事業所の介護職員が集計に含まれていない。提出の有無を確認する。第2章第6節（人材）の従事者数に影響する。</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>第3章第5節</t>
+          <t>第2章第6節</t>
         </is>
       </c>
     </row>
@@ -13456,7 +13456,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>施設単位の介護職員数が、その施設の入居者に提供される介護の量を表さない。第3章第5節で施設種別ごとの職員配置を記述する際は、住まいと介護サービスの提供主体が別であることを注記する。</t>
+          <t>施設単位の介護職員数が、その施設の入居者に提供される介護の量を表さない。第2章第6節で施設種別ごとの職員配置を記述する際は、住まいと介護サービスの提供主体が別であることを注記する。</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -13471,7 +13471,7 @@
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>第3章第5節</t>
+          <t>第2章第6節</t>
         </is>
       </c>
     </row>
@@ -13546,7 +13546,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>①調査で「介護職員」に支援相談員・その他の職員を含めて記入したのか、②見える化の令和5・6年度の値が実態より低いのかを確認する。第3章第5節では「介護老人福祉施設の従事者数は平成29年度116人から令和6年度105人へ9.5％減少」と記述しており、老健の従事者数の推移を同じ枠組みで記述できるかどうかが変わる。調査票の職種の範囲を事業所に照会する。</t>
+          <t>①調査で「介護職員」に支援相談員・その他の職員を含めて記入したのか、②見える化の令和5・6年度の値が実態より低いのかを確認する。第2章第6節では「介護老人福祉施設の従事者数は平成29年度116人から令和6年度105人へ9.5％減少」と記述しており、老健の従事者数の推移を同じ枠組みで記述できるかどうかが変わる。調査票の職種の範囲を事業所に照会する。</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -13561,7 +13561,7 @@
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>第3章第5節</t>
+          <t>第2章第6節</t>
         </is>
       </c>
     </row>
@@ -13741,14 +13741,14 @@
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>第2章第3節、第7章第1節</t>
+          <t>第2章第3節</t>
         </is>
       </c>
     </row>
     <row r="41" ht="104" customHeight="1">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>注1）重大6件は、集計の方法を決めないと計画本文に載せる数値が変わるものである。No.1は介護職員の総数、No.2は小規模多機能の見込量、No.3は地区別分析の可否、No.31は従事者数の推移の記述に直結する。注2）要確認21件は、事業所への照会により解消できる見込みである。照会の要否と方法は発注者のご意向を確認する。注3）様式・網羅性8件は、今回の調査票が第9期の様式を踏襲していることによるものであり、今回の集計を止めるものではない。第11期以降の様式の見直しの材料として記録する。注4）確認主体・確認の期限は重要度による既定値であり、個別に定めるものは上書きしている。反映先は取扱い欄に記載した計画素案の章節を機械的に抽出したものである。本シートが未確定事項の内部管理版であり、「実施済み調査 結果報告書」（Word）の未確定事項表は本シートを要約したものである。</t>
+          <t>注1）重大6件は、集計の方法を決めないと計画本文に載せる数値が変わるものである。No.1は介護職員の総数、No.2は小規模多機能の見込量、No.3は地区別分析の可否、No.31は従事者数の推移の記述に直結する。注2）要確認21件は、事業所への照会により解消できる見込みである。照会の要否と方法は発注者のご意向を確認する。注3）様式・網羅性8件は、今回の調査票が第9期の様式を踏襲していることによるものであり、今回の集計を止めるものではない。第11期以降の様式の見直しの材料として記録する。注4）確認主体・確認の期限は重要度による既定値であり、個別に定めるものは上書きしている。反映先は取扱い欄に記載した計画素案の章節を機械的に抽出したものである。計画素案に実在しない章節は掲げていない。「実施済み調査 結果報告書」（Word）の未確定事項の表は本シートを要約したものである。</t>
         </is>
       </c>
     </row>
@@ -20363,7 +20363,7 @@
     <row r="40" ht="104" customHeight="1">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>注1）介護職員は施設・通所系319人・訪問系42人の計361人であるが、No.1の重複を除くと348人となる。第3章第5節（介護人材）で用いる際は、重複の確認を経た数値による。注2）外国人職員は施設・通所系で37人であり、介護職員319人の11.6％を占める。24事業所のうち13事業所に配置されており、グループホームゆう8人、特別養護老人ホーム美瑛慈光園5人、有料老人ホームゆう4人の順に多い。訪問系では0人である。注3）派遣職員は1人（老人保健施設ひだまりの里）である。ただし6事業所で未記入であり、0人と未記入の区別がつかない。注4）採用90人・離職67人であり、差は23人である（No.1の重複を含む。重複を除くと採用83人・離職65人、差18人）。注5）職員個票は施設・通所系のみの様式であり、訪問系は職員1人につき1ファイルの職員票による（07シート）。</t>
+          <t>注1）介護職員は施設・通所系319人・訪問系42人の計361人であるが、No.1の重複を除くと348人となる。第2章第6節（介護人材）で用いる際は、重複の確認を経た数値による。注2）外国人職員は施設・通所系で37人であり、介護職員319人の11.6％を占める。24事業所のうち13事業所に配置されており、グループホームゆう8人、特別養護老人ホーム美瑛慈光園5人、有料老人ホームゆう4人の順に多い。訪問系では0人である。注3）派遣職員は1人（老人保健施設ひだまりの里）である。ただし6事業所で未記入であり、0人と未記入の区別がつかない。注4）採用90人・離職67人であり、差は23人である（No.1の重複を含む。重複を除くと採用83人・離職65人、差18人）。注5）職員個票は施設・通所系のみの様式であり、訪問系は職員1人につき1ファイルの職員票による（07シート）。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
+++ b/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
@@ -1286,7 +1286,7 @@
       </c>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t>着手可</t>
+          <t>反映済</t>
         </is>
       </c>
     </row>
@@ -1316,14 +1316,14 @@
       </c>
       <c r="F13" s="21" t="inlineStr">
         <is>
-          <t>着手可</t>
+          <t>反映済</t>
         </is>
       </c>
     </row>
     <row r="15" ht="104" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>注1）No.8（住まいの供給量）とNo.9（医療と介護の連携）は、点検で見つかった事項の影響を受けずに着手できる。No.8は北海道の名簿により定員を確定できるようになったため、確認待ちから着手可に改めた。残る7件は重大6件又は要確認の解消を待つ。注2）本シートの反映方針は受託者の案であり、仕様書の定めにより業務工程の都度発注者のご意向を確認する。特にNo.2（「市内／市外」の定義）とNo.6（小規模多機能の偏りの取扱い）は、計画本文の数値が変わるため、ご意向を確認したうえで反映する。注3）事業所への照会を行う場合の照会先・照会方法・期限は、発注者と協議のうえ定める。受託者が直接照会するか、広域連合を通じるかを確認する。</t>
+          <t>注1）No.8（住まいの供給量）とNo.9（医療と介護の連携）は、点検で見つかった事項の影響を受けずに進められるものであり、作業を継続して計画素案への反映を完了した（No.8は第2章第3節の区域内の施設・住まいの一覧に定員を掲載する形で、No.9は第6章第5節に入所前の居場所と退去先の割合を掲載する形で反映した）。No.8の入居者数は4施設分しか把握できていないため、定員のみの掲載としている。残る7件は重大6件又は要確認の解消を待つ。注2）本シートの反映方針は受託者の案であり、仕様書の定めにより業務工程の都度発注者のご意向を確認する。特にNo.2（「市内／市外」の定義）とNo.6（小規模多機能の偏りの取扱い）は、計画本文の数値が変わるため、ご意向を確認したうえで反映する。注3）事業所への照会を行う場合の照会先・照会方法・期限は、発注者と協議のうえ定める。受託者が直接照会するか、広域連合を通じるかを確認する。</t>
         </is>
       </c>
     </row>
